--- a/fixtures/sml/cell/boolean-true.xlsx
+++ b/fixtures/sml/cell/boolean-true.xlsx
@@ -10,8 +10,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
-    <row r="0">
-      <c r="0" t="b">
+    <row r="1">
+      <c r="A1" t="b">
         <v>1</v>
       </c>
     </row>
